--- a/sheets/대금율보/검수/애수의 가을밤.xlsx
+++ b/sheets/대금율보/검수/애수의 가을밤.xlsx
@@ -5304,32 +5304,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="119.22" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="119.22" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="119.22" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="119.22" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="119.22" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="119.22" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="119.22" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="119.22" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
       <c r="T10" s="21"/>
       <c r="U10" s="23"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="119.22" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="U11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="119.22" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="119.22" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="119.22" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -6401,10 +6401,10 @@
       </c>
       <c r="U14" s="24"/>
     </row>
-    <row r="15">
+    <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="80.0" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="119.22" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -6472,7 +6472,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="119.22" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="23"/>
@@ -6511,7 +6511,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="119.22" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="24"/>
@@ -6552,7 +6552,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="119.22" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -6592,7 +6592,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="119.22" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -6632,7 +6632,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="119.22" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="24"/>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="119.22" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -6711,7 +6711,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="119.22" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="119.22" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -6775,7 +6775,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="119.22" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -6806,7 +6806,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="119.22" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -6829,7 +6829,7 @@
       <c r="T27" s="21"/>
       <c r="U27" s="23"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="119.22" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="24"/>
@@ -6868,7 +6868,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="14" max="16383" man="1"/>
   </rowBreaks>
